--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067035</v>
+        <v>131067787</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +817,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466172</v>
+        <v>466335</v>
       </c>
       <c r="R3" t="n">
-        <v>7046340</v>
+        <v>7046445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +898,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,14 +916,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067787</v>
+        <v>131067798</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -980,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466335</v>
+        <v>466279</v>
       </c>
       <c r="R4" t="n">
-        <v>7046445</v>
+        <v>7046403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1197,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067810</v>
+        <v>131067035</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,50 +1207,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466532</v>
+        <v>466172</v>
       </c>
       <c r="R6" t="n">
-        <v>7046605</v>
+        <v>7046340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1274,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,12 +1283,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067798</v>
+        <v>131067810</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,42 +1338,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466279</v>
+        <v>466532</v>
       </c>
       <c r="R7" t="n">
-        <v>7046403</v>
+        <v>7046605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,7 +1418,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,22 +1432,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067030</v>
+        <v>131067786</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,26 +1726,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1753,10 +1758,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466302</v>
+        <v>466366</v>
       </c>
       <c r="R10" t="n">
-        <v>7046517</v>
+        <v>7046466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1791,13 +1796,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1816,14 +1825,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1841,7 +1845,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067786</v>
+        <v>131067792</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1874,7 +1878,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1884,10 +1888,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466366</v>
+        <v>466356</v>
       </c>
       <c r="R11" t="n">
-        <v>7046466</v>
+        <v>7046460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1928,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,9 +1955,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1971,7 +1980,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067792</v>
+        <v>131067781</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -2004,7 +2013,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2014,10 +2023,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466356</v>
+        <v>466204</v>
       </c>
       <c r="R12" t="n">
-        <v>7046460</v>
+        <v>7046448</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,7 +2063,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,7 +2077,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2081,14 +2090,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2106,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131067781</v>
+        <v>131067030</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,31 +2121,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2149,10 +2148,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466204</v>
+        <v>466302</v>
       </c>
       <c r="R13" t="n">
-        <v>7046448</v>
+        <v>7046517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2187,23 +2186,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2216,9 +2211,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067803</v>
+        <v>131067782</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466227</v>
+        <v>466553</v>
       </c>
       <c r="R23" t="n">
-        <v>7046368</v>
+        <v>7046611</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3520,14 +3520,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,7 +3540,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067782</v>
+        <v>131067803</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -3588,10 +3583,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466553</v>
+        <v>466227</v>
       </c>
       <c r="R24" t="n">
-        <v>7046611</v>
+        <v>7046368</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3642,7 +3637,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3655,9 +3650,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067038</v>
+        <v>131067797</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3937,26 +3937,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3964,10 +3969,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466024</v>
+        <v>466283</v>
       </c>
       <c r="R27" t="n">
-        <v>7046276</v>
+        <v>7046407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4004,7 +4009,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4013,7 +4018,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4032,14 +4036,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4057,7 +4056,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067797</v>
+        <v>131067806</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -4090,7 +4089,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4100,10 +4099,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466283</v>
+        <v>466140</v>
       </c>
       <c r="R28" t="n">
-        <v>7046407</v>
+        <v>7046291</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4140,7 +4139,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4167,9 +4166,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4187,10 +4191,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067806</v>
+        <v>131067038</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4198,31 +4202,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4230,10 +4229,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466140</v>
+        <v>466024</v>
       </c>
       <c r="R29" t="n">
-        <v>7046291</v>
+        <v>7046276</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4270,7 +4269,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4279,6 +4278,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4299,12 +4299,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5167,7 +5167,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067031</v>
+        <v>131067032</v>
       </c>
       <c r="B37" t="n">
         <v>79244</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466288</v>
+        <v>466239</v>
       </c>
       <c r="R37" t="n">
-        <v>7046458</v>
+        <v>7046392</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5241,11 +5241,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5298,7 +5293,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067032</v>
+        <v>131067031</v>
       </c>
       <c r="B38" t="n">
         <v>79244</v>
@@ -5336,10 +5331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466239</v>
+        <v>466288</v>
       </c>
       <c r="R38" t="n">
-        <v>7046392</v>
+        <v>7046458</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5372,6 +5367,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -1196,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067035</v>
+        <v>131067810</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,37 +1207,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466172</v>
+        <v>466532</v>
       </c>
       <c r="R6" t="n">
-        <v>7046340</v>
+        <v>7046605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,33 +1296,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1327,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067810</v>
+        <v>131067035</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,50 +1330,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466532</v>
+        <v>466172</v>
       </c>
       <c r="R7" t="n">
-        <v>7046605</v>
+        <v>7046340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,7 +1397,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,12 +1406,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067786</v>
+        <v>131067030</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,31 +1726,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466366</v>
+        <v>466302</v>
       </c>
       <c r="R10" t="n">
-        <v>7046466</v>
+        <v>7046517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1796,17 +1791,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1825,9 +1816,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1845,7 +1841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067792</v>
+        <v>131067786</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1878,7 +1874,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1888,10 +1884,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466356</v>
+        <v>466366</v>
       </c>
       <c r="R11" t="n">
-        <v>7046460</v>
+        <v>7046466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1928,7 +1924,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,14 +1951,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1980,7 +1971,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067781</v>
+        <v>131067792</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -2013,7 +2004,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2023,10 +2014,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466204</v>
+        <v>466356</v>
       </c>
       <c r="R12" t="n">
-        <v>7046448</v>
+        <v>7046460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2063,7 +2054,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +2068,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2090,9 +2081,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2110,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131067030</v>
+        <v>131067781</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,26 +2117,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2148,10 +2149,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466302</v>
+        <v>466204</v>
       </c>
       <c r="R13" t="n">
-        <v>7046517</v>
+        <v>7046448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2186,19 +2187,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2211,14 +2216,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -5167,7 +5167,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067032</v>
+        <v>131067031</v>
       </c>
       <c r="B37" t="n">
         <v>79244</v>
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466239</v>
+        <v>466288</v>
       </c>
       <c r="R37" t="n">
-        <v>7046392</v>
+        <v>7046458</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5241,6 +5241,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5293,7 +5298,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067031</v>
+        <v>131067032</v>
       </c>
       <c r="B38" t="n">
         <v>79244</v>
@@ -5331,10 +5336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466288</v>
+        <v>466239</v>
       </c>
       <c r="R38" t="n">
-        <v>7046458</v>
+        <v>7046392</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5367,11 +5372,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5424,32 +5424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067790</v>
+        <v>131067006</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>57073</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5457,20 +5457,24 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466313</v>
+        <v>466180</v>
       </c>
       <c r="R39" t="n">
-        <v>7046432</v>
+        <v>7046368</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5507,7 +5511,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5522,21 +5526,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5554,7 +5543,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067789</v>
+        <v>131067790</v>
       </c>
       <c r="B40" t="n">
         <v>57884</v>
@@ -5597,10 +5586,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466317</v>
+        <v>466313</v>
       </c>
       <c r="R40" t="n">
-        <v>7046435</v>
+        <v>7046432</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5684,32 +5673,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067006</v>
+        <v>131067789</v>
       </c>
       <c r="B41" t="n">
-        <v>57073</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5717,24 +5706,20 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466180</v>
+        <v>466317</v>
       </c>
       <c r="R41" t="n">
-        <v>7046368</v>
+        <v>7046435</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5771,7 +5756,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5786,6 +5771,21 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067787</v>
+        <v>131067035</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,31 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466335</v>
+        <v>466172</v>
       </c>
       <c r="R3" t="n">
-        <v>7046445</v>
+        <v>7046340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,9 +912,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067798</v>
+        <v>131067810</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,42 +948,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466279</v>
+        <v>466532</v>
       </c>
       <c r="R4" t="n">
-        <v>7046403</v>
+        <v>7046605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,22 +1042,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,7 +1060,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067788</v>
+        <v>131067787</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1109,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466325</v>
+        <v>466335</v>
       </c>
       <c r="R5" t="n">
-        <v>7046442</v>
+        <v>7046445</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1196,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067810</v>
+        <v>131067798</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,50 +1201,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466532</v>
+        <v>466279</v>
       </c>
       <c r="R6" t="n">
-        <v>7046605</v>
+        <v>7046403</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1273,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1287,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067035</v>
+        <v>131067788</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,26 +1331,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1357,10 +1363,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466172</v>
+        <v>466325</v>
       </c>
       <c r="R7" t="n">
-        <v>7046340</v>
+        <v>7046442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,7 +1403,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,7 +1412,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1425,14 +1430,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067797</v>
+        <v>131067038</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3937,31 +3937,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3969,10 +3964,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466283</v>
+        <v>466024</v>
       </c>
       <c r="R27" t="n">
-        <v>7046407</v>
+        <v>7046276</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4009,7 +4004,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4018,6 +4013,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4036,9 +4032,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4056,7 +4057,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067806</v>
+        <v>131067797</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -4089,7 +4090,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4099,10 +4100,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466140</v>
+        <v>466283</v>
       </c>
       <c r="R28" t="n">
-        <v>7046291</v>
+        <v>7046407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4139,7 +4140,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,14 +4167,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4191,10 +4187,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067038</v>
+        <v>131067806</v>
       </c>
       <c r="B29" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4202,26 +4198,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4229,10 +4230,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466024</v>
+        <v>466140</v>
       </c>
       <c r="R29" t="n">
-        <v>7046276</v>
+        <v>7046291</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4269,7 +4270,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,7 +4279,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4299,12 +4299,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067036</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131067035</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067810</v>
+        <v>131067787</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,50 +948,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466532</v>
+        <v>466335</v>
       </c>
       <c r="R4" t="n">
-        <v>7046605</v>
+        <v>7046445</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1020,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,6 +1035,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,7 +1067,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067787</v>
+        <v>131067798</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1103,10 +1110,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466335</v>
+        <v>466279</v>
       </c>
       <c r="R5" t="n">
-        <v>7046445</v>
+        <v>7046403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,7 +1164,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1190,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067798</v>
+        <v>131067788</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1233,10 +1240,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466279</v>
+        <v>466325</v>
       </c>
       <c r="R6" t="n">
-        <v>7046403</v>
+        <v>7046442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1294,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067788</v>
+        <v>131067810</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,42 +1338,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466325</v>
+        <v>466532</v>
       </c>
       <c r="R7" t="n">
-        <v>7046442</v>
+        <v>7046605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,7 +1418,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,21 +1433,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067030</v>
+        <v>131067786</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,26 +1726,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1753,10 +1758,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466302</v>
+        <v>466366</v>
       </c>
       <c r="R10" t="n">
-        <v>7046517</v>
+        <v>7046466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1791,13 +1796,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1816,14 +1825,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1841,7 +1845,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067786</v>
+        <v>131067792</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1874,7 +1878,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1884,10 +1888,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466366</v>
+        <v>466356</v>
       </c>
       <c r="R11" t="n">
-        <v>7046466</v>
+        <v>7046460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1928,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,9 +1955,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1971,7 +1980,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067792</v>
+        <v>131067781</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -2004,7 +2013,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2014,10 +2023,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466356</v>
+        <v>466204</v>
       </c>
       <c r="R12" t="n">
-        <v>7046460</v>
+        <v>7046448</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,7 +2063,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,7 +2077,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2081,14 +2090,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2106,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131067781</v>
+        <v>131067030</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,31 +2121,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2149,10 +2148,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466204</v>
+        <v>466302</v>
       </c>
       <c r="R13" t="n">
-        <v>7046448</v>
+        <v>7046517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2187,23 +2186,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2216,9 +2211,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3813,7 +3813,7 @@
         <v>131067453</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>131067038</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>131067452</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>131067033</v>
       </c>
       <c r="B31" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>131067037</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>131067451</v>
       </c>
       <c r="B36" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>131067031</v>
       </c>
       <c r="B37" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>131067032</v>
       </c>
       <c r="B38" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5424,32 +5424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067006</v>
+        <v>131067790</v>
       </c>
       <c r="B39" t="n">
-        <v>57073</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5457,24 +5457,20 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466180</v>
+        <v>466313</v>
       </c>
       <c r="R39" t="n">
-        <v>7046368</v>
+        <v>7046432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5511,7 +5507,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5526,6 +5522,21 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5543,7 +5554,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067790</v>
+        <v>131067789</v>
       </c>
       <c r="B40" t="n">
         <v>57884</v>
@@ -5586,10 +5597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466313</v>
+        <v>466317</v>
       </c>
       <c r="R40" t="n">
-        <v>7046432</v>
+        <v>7046435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5673,32 +5684,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067789</v>
+        <v>131067006</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>57073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5706,20 +5717,24 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466317</v>
+        <v>466180</v>
       </c>
       <c r="R41" t="n">
-        <v>7046435</v>
+        <v>7046368</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5756,7 +5771,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5771,21 +5786,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067035</v>
+        <v>131067810</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +817,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466172</v>
+        <v>466532</v>
       </c>
       <c r="R3" t="n">
-        <v>7046340</v>
+        <v>7046605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,33 +906,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067787</v>
+        <v>131067035</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,31 +940,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466335</v>
+        <v>466172</v>
       </c>
       <c r="R4" t="n">
-        <v>7046445</v>
+        <v>7046340</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1007,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,6 +1016,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1047,9 +1035,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,7 +1060,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067798</v>
+        <v>131067787</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1110,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466279</v>
+        <v>466335</v>
       </c>
       <c r="R5" t="n">
-        <v>7046403</v>
+        <v>7046445</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1164,7 +1157,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1197,7 +1190,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067788</v>
+        <v>131067798</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1240,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466325</v>
+        <v>466279</v>
       </c>
       <c r="R6" t="n">
-        <v>7046442</v>
+        <v>7046403</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1287,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1327,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067810</v>
+        <v>131067788</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,50 +1331,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466532</v>
+        <v>466325</v>
       </c>
       <c r="R7" t="n">
-        <v>7046605</v>
+        <v>7046442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,7 +1403,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,6 +1418,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067786</v>
+        <v>131067030</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,31 +1726,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466366</v>
+        <v>466302</v>
       </c>
       <c r="R10" t="n">
-        <v>7046466</v>
+        <v>7046517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1796,17 +1791,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1825,9 +1816,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1845,7 +1841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067792</v>
+        <v>131067786</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1878,7 +1874,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1888,10 +1884,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466356</v>
+        <v>466366</v>
       </c>
       <c r="R11" t="n">
-        <v>7046460</v>
+        <v>7046466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1928,7 +1924,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,14 +1951,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1980,7 +1971,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067781</v>
+        <v>131067792</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -2013,7 +2004,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2023,10 +2014,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466204</v>
+        <v>466356</v>
       </c>
       <c r="R12" t="n">
-        <v>7046448</v>
+        <v>7046460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2063,7 +2054,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +2068,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2090,9 +2081,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2110,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131067030</v>
+        <v>131067781</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,26 +2117,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2148,10 +2149,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466302</v>
+        <v>466204</v>
       </c>
       <c r="R13" t="n">
-        <v>7046517</v>
+        <v>7046448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2186,19 +2187,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2211,14 +2216,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067033</v>
+        <v>131067804</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,26 +4449,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4476,10 +4481,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466193</v>
+        <v>466158</v>
       </c>
       <c r="R31" t="n">
-        <v>7046386</v>
+        <v>7046307</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4516,7 +4521,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4525,13 +4530,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4549,7 +4573,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067804</v>
+        <v>131067784</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4592,10 +4616,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466158</v>
+        <v>466379</v>
       </c>
       <c r="R32" t="n">
-        <v>7046307</v>
+        <v>7046479</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4646,7 +4670,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4659,14 +4683,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4684,7 +4703,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067784</v>
+        <v>131067793</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4727,10 +4746,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466379</v>
+        <v>466303</v>
       </c>
       <c r="R33" t="n">
-        <v>7046479</v>
+        <v>7046416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4781,7 +4800,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4814,10 +4833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067793</v>
+        <v>131067033</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4825,31 +4844,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4857,10 +4871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466303</v>
+        <v>466193</v>
       </c>
       <c r="R34" t="n">
-        <v>7046416</v>
+        <v>7046386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4897,7 +4911,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4906,27 +4920,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067810</v>
+        <v>131067035</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,50 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466532</v>
+        <v>466172</v>
       </c>
       <c r="R3" t="n">
-        <v>7046605</v>
+        <v>7046340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +893,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067035</v>
+        <v>131067787</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,26 +948,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466172</v>
+        <v>466335</v>
       </c>
       <c r="R4" t="n">
-        <v>7046340</v>
+        <v>7046445</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1020,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1029,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1035,14 +1047,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,7 +1067,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067787</v>
+        <v>131067798</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1103,10 +1110,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466335</v>
+        <v>466279</v>
       </c>
       <c r="R5" t="n">
-        <v>7046445</v>
+        <v>7046403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,7 +1164,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1190,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067798</v>
+        <v>131067788</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1233,10 +1240,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466279</v>
+        <v>466325</v>
       </c>
       <c r="R6" t="n">
-        <v>7046403</v>
+        <v>7046442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1294,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067788</v>
+        <v>131067810</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,42 +1338,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466325</v>
+        <v>466532</v>
       </c>
       <c r="R7" t="n">
-        <v>7046442</v>
+        <v>7046605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,7 +1418,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,21 +1433,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067804</v>
+        <v>131067033</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,31 +4449,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4481,10 +4476,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466158</v>
+        <v>466193</v>
       </c>
       <c r="R31" t="n">
-        <v>7046307</v>
+        <v>7046386</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4521,7 +4516,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4530,32 +4525,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4573,7 +4549,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067784</v>
+        <v>131067804</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4616,10 +4592,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466379</v>
+        <v>466158</v>
       </c>
       <c r="R32" t="n">
-        <v>7046479</v>
+        <v>7046307</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4670,7 +4646,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4683,9 +4659,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4703,7 +4684,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067793</v>
+        <v>131067784</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4746,10 +4727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466303</v>
+        <v>466379</v>
       </c>
       <c r="R33" t="n">
-        <v>7046416</v>
+        <v>7046479</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4800,7 +4781,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4833,10 +4814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067033</v>
+        <v>131067793</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4844,26 +4825,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4871,10 +4857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466193</v>
+        <v>466303</v>
       </c>
       <c r="R34" t="n">
-        <v>7046386</v>
+        <v>7046416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4911,7 +4897,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4920,13 +4906,27 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -5167,48 +5167,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067031</v>
+        <v>131067006</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>57073</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466288</v>
+        <v>466180</v>
       </c>
       <c r="R37" t="n">
-        <v>7046458</v>
+        <v>7046368</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5245,7 +5254,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera gamla granar i granskog.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5254,33 +5263,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5298,7 +5286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067032</v>
+        <v>131067031</v>
       </c>
       <c r="B38" t="n">
         <v>79245</v>
@@ -5336,10 +5324,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466239</v>
+        <v>466288</v>
       </c>
       <c r="R38" t="n">
-        <v>7046392</v>
+        <v>7046458</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5372,6 +5360,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5424,10 +5417,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067790</v>
+        <v>131067032</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5435,31 +5428,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5467,10 +5455,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466313</v>
+        <v>466239</v>
       </c>
       <c r="R39" t="n">
-        <v>7046432</v>
+        <v>7046392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5505,23 +5493,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5534,9 +5518,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5554,7 +5543,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067789</v>
+        <v>131067790</v>
       </c>
       <c r="B40" t="n">
         <v>57884</v>
@@ -5597,10 +5586,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466317</v>
+        <v>466313</v>
       </c>
       <c r="R40" t="n">
-        <v>7046435</v>
+        <v>7046432</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5684,32 +5673,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067006</v>
+        <v>131067789</v>
       </c>
       <c r="B41" t="n">
-        <v>57073</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5717,24 +5706,20 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466180</v>
+        <v>466317</v>
       </c>
       <c r="R41" t="n">
-        <v>7046368</v>
+        <v>7046435</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5771,7 +5756,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5786,6 +5771,21 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067036</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067035</v>
+        <v>131067787</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +817,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466172</v>
+        <v>466335</v>
       </c>
       <c r="R3" t="n">
-        <v>7046340</v>
+        <v>7046445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +898,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,14 +916,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067787</v>
+        <v>131067798</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -980,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466335</v>
+        <v>466279</v>
       </c>
       <c r="R4" t="n">
-        <v>7046445</v>
+        <v>7046403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1067,7 +1066,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067798</v>
+        <v>131067788</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1110,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466279</v>
+        <v>466325</v>
       </c>
       <c r="R5" t="n">
-        <v>7046403</v>
+        <v>7046442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1164,7 +1163,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1197,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067788</v>
+        <v>131067810</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,42 +1207,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466325</v>
+        <v>466532</v>
       </c>
       <c r="R6" t="n">
-        <v>7046442</v>
+        <v>7046605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,21 +1302,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1327,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067810</v>
+        <v>131067035</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,50 +1330,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466532</v>
+        <v>466172</v>
       </c>
       <c r="R7" t="n">
-        <v>7046605</v>
+        <v>7046340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,7 +1397,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,12 +1406,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
         <v>131067030</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>131067453</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>131067038</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>131067452</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067033</v>
+        <v>131067804</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,26 +4449,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4476,10 +4481,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466193</v>
+        <v>466158</v>
       </c>
       <c r="R31" t="n">
-        <v>7046386</v>
+        <v>7046307</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4516,7 +4521,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4525,13 +4530,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4549,7 +4573,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067804</v>
+        <v>131067784</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4592,10 +4616,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466158</v>
+        <v>466379</v>
       </c>
       <c r="R32" t="n">
-        <v>7046307</v>
+        <v>7046479</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4646,7 +4670,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4659,14 +4683,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4684,7 +4703,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067784</v>
+        <v>131067793</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4727,10 +4746,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466379</v>
+        <v>466303</v>
       </c>
       <c r="R33" t="n">
-        <v>7046479</v>
+        <v>7046416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4781,7 +4800,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4814,10 +4833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067793</v>
+        <v>131067033</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4825,31 +4844,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4857,10 +4871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466303</v>
+        <v>466193</v>
       </c>
       <c r="R34" t="n">
-        <v>7046416</v>
+        <v>7046386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4897,7 +4911,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4906,27 +4920,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4947,7 +4947,7 @@
         <v>131067037</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>131067451</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5167,32 +5167,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067006</v>
+        <v>131067790</v>
       </c>
       <c r="B37" t="n">
-        <v>57073</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5200,24 +5200,20 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466180</v>
+        <v>466313</v>
       </c>
       <c r="R37" t="n">
-        <v>7046368</v>
+        <v>7046432</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5254,7 +5250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5269,6 +5265,21 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5286,10 +5297,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067031</v>
+        <v>131067789</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5297,26 +5308,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5324,10 +5340,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466288</v>
+        <v>466317</v>
       </c>
       <c r="R38" t="n">
-        <v>7046458</v>
+        <v>7046435</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5364,7 +5380,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På flera gamla granar i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5373,13 +5389,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5392,14 +5407,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5417,48 +5427,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067032</v>
+        <v>131067006</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>57073</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466239</v>
+        <v>466180</v>
       </c>
       <c r="R39" t="n">
-        <v>7046392</v>
+        <v>7046368</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5493,39 +5512,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5543,10 +5546,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067790</v>
+        <v>131067031</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5554,31 +5557,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5586,10 +5584,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466313</v>
+        <v>466288</v>
       </c>
       <c r="R40" t="n">
-        <v>7046432</v>
+        <v>7046458</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5626,7 +5624,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5635,12 +5633,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5653,9 +5652,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5673,10 +5677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067789</v>
+        <v>131067032</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5684,31 +5688,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5716,10 +5715,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466317</v>
+        <v>466239</v>
       </c>
       <c r="R41" t="n">
-        <v>7046435</v>
+        <v>7046392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5754,23 +5753,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5783,9 +5778,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -4438,10 +4438,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067804</v>
+        <v>131067033</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,31 +4449,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4481,10 +4476,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466158</v>
+        <v>466193</v>
       </c>
       <c r="R31" t="n">
-        <v>7046307</v>
+        <v>7046386</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4521,7 +4516,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4530,32 +4525,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4573,7 +4549,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067784</v>
+        <v>131067804</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -4616,10 +4592,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466379</v>
+        <v>466158</v>
       </c>
       <c r="R32" t="n">
-        <v>7046479</v>
+        <v>7046307</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4670,7 +4646,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4683,9 +4659,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4703,7 +4684,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067793</v>
+        <v>131067784</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -4746,10 +4727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466303</v>
+        <v>466379</v>
       </c>
       <c r="R33" t="n">
-        <v>7046416</v>
+        <v>7046479</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4800,7 +4781,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4833,10 +4814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067033</v>
+        <v>131067793</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4844,26 +4825,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4871,10 +4857,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466193</v>
+        <v>466303</v>
       </c>
       <c r="R34" t="n">
-        <v>7046386</v>
+        <v>7046416</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4911,7 +4897,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4920,13 +4906,27 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5427,57 +5427,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067006</v>
+        <v>131067031</v>
       </c>
       <c r="B39" t="n">
-        <v>57073</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466180</v>
+        <v>466288</v>
       </c>
       <c r="R39" t="n">
-        <v>7046368</v>
+        <v>7046458</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5514,7 +5505,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5523,12 +5514,33 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5546,7 +5558,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067031</v>
+        <v>131067032</v>
       </c>
       <c r="B40" t="n">
         <v>79246</v>
@@ -5584,10 +5596,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466288</v>
+        <v>466239</v>
       </c>
       <c r="R40" t="n">
-        <v>7046458</v>
+        <v>7046392</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5620,11 +5632,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5677,48 +5684,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067032</v>
+        <v>131067006</v>
       </c>
       <c r="B41" t="n">
-        <v>79246</v>
+        <v>57073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466239</v>
+        <v>466180</v>
       </c>
       <c r="R41" t="n">
-        <v>7046392</v>
+        <v>7046368</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5753,39 +5769,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067036</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131067787</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131067798</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067788</v>
+        <v>131067035</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,31 +1077,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466325</v>
+        <v>466172</v>
       </c>
       <c r="R5" t="n">
-        <v>7046442</v>
+        <v>7046340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,6 +1153,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,9 +1172,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1196,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067810</v>
+        <v>131067788</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,50 +1208,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466532</v>
+        <v>466325</v>
       </c>
       <c r="R6" t="n">
-        <v>7046605</v>
+        <v>7046442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1280,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1295,21 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067035</v>
+        <v>131067810</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,37 +1338,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466172</v>
+        <v>466532</v>
       </c>
       <c r="R7" t="n">
-        <v>7046340</v>
+        <v>7046605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,7 +1418,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,33 +1427,12 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
         <v>131067801</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131067000</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131067030</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>131067786</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>131067792</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>131067781</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>131067800</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>131067795</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131067799</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>131067005</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067783</v>
+        <v>131067805</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466431</v>
+        <v>466148</v>
       </c>
       <c r="R18" t="n">
-        <v>7046517</v>
+        <v>7046298</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2860,9 +2860,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2880,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067805</v>
+        <v>131067783</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2923,10 +2928,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466148</v>
+        <v>466431</v>
       </c>
       <c r="R19" t="n">
-        <v>7046298</v>
+        <v>7046517</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,7 +2982,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2990,14 +2995,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>131067802</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>131067791</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>131067794</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>131067782</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>131067803</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>131067796</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>131067453</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>131067038</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>131067797</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>131067806</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>131067452</v>
       </c>
       <c r="B30" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>131067033</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>131067804</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>131067784</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>131067793</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>131067037</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>131067451</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>131067790</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5297,32 +5297,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067789</v>
+        <v>131067006</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>57075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5330,20 +5330,24 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466317</v>
+        <v>466180</v>
       </c>
       <c r="R38" t="n">
-        <v>7046435</v>
+        <v>7046368</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5380,7 +5384,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5395,21 +5399,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5430,7 +5419,7 @@
         <v>131067031</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,7 +5550,7 @@
         <v>131067032</v>
       </c>
       <c r="B40" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5684,32 +5673,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067006</v>
+        <v>131067789</v>
       </c>
       <c r="B41" t="n">
-        <v>57073</v>
+        <v>57886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5717,24 +5706,20 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466180</v>
+        <v>466317</v>
       </c>
       <c r="R41" t="n">
-        <v>7046368</v>
+        <v>7046435</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5771,7 +5756,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5786,6 +5771,21 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067036</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131067787</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>131067798</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067035</v>
+        <v>131067788</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,26 +1077,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466172</v>
+        <v>466325</v>
       </c>
       <c r="R5" t="n">
-        <v>7046340</v>
+        <v>7046442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1158,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1172,14 +1176,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067788</v>
+        <v>131067035</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,31 +1207,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1240,10 +1234,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466325</v>
+        <v>466172</v>
       </c>
       <c r="R6" t="n">
-        <v>7046442</v>
+        <v>7046340</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1274,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,6 +1283,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1307,9 +1302,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>131067810</v>
       </c>
       <c r="B7" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>131067801</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131067000</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067030</v>
+        <v>131067786</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,26 +1726,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1753,10 +1758,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466302</v>
+        <v>466366</v>
       </c>
       <c r="R10" t="n">
-        <v>7046517</v>
+        <v>7046466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1791,13 +1796,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1816,14 +1825,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1841,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067786</v>
+        <v>131067792</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1878,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1884,10 +1888,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466366</v>
+        <v>466356</v>
       </c>
       <c r="R11" t="n">
-        <v>7046466</v>
+        <v>7046460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1928,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,9 +1955,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1971,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067792</v>
+        <v>131067781</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,7 +2013,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2014,10 +2023,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466356</v>
+        <v>466204</v>
       </c>
       <c r="R12" t="n">
-        <v>7046460</v>
+        <v>7046448</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,7 +2063,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,7 +2077,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2081,14 +2090,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2106,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131067781</v>
+        <v>131067030</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,31 +2121,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2149,10 +2148,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466204</v>
+        <v>466302</v>
       </c>
       <c r="R13" t="n">
-        <v>7046448</v>
+        <v>7046517</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2187,23 +2186,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2216,9 +2211,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
         <v>131067800</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>131067795</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131067799</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>131067005</v>
       </c>
       <c r="B17" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067805</v>
+        <v>131067783</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466148</v>
+        <v>466431</v>
       </c>
       <c r="R18" t="n">
-        <v>7046298</v>
+        <v>7046517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2860,14 +2860,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2885,10 +2880,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067783</v>
+        <v>131067805</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2928,10 +2923,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466431</v>
+        <v>466148</v>
       </c>
       <c r="R19" t="n">
-        <v>7046517</v>
+        <v>7046298</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2982,7 +2977,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2995,9 +2990,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>131067802</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>131067791</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>131067794</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>131067782</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>131067803</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>131067796</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>131067453</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>131067038</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>131067797</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>131067806</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>131067452</v>
       </c>
       <c r="B30" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>131067033</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>131067804</v>
       </c>
       <c r="B32" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>131067784</v>
       </c>
       <c r="B33" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>131067793</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>131067037</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>131067451</v>
       </c>
       <c r="B36" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5167,10 +5167,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067790</v>
+        <v>131067031</v>
       </c>
       <c r="B37" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5178,31 +5178,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5210,10 +5205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466313</v>
+        <v>466288</v>
       </c>
       <c r="R37" t="n">
-        <v>7046432</v>
+        <v>7046458</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5250,7 +5245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5259,12 +5254,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5277,9 +5273,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5297,57 +5298,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067006</v>
+        <v>131067032</v>
       </c>
       <c r="B38" t="n">
-        <v>57075</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466180</v>
+        <v>466239</v>
       </c>
       <c r="R38" t="n">
-        <v>7046368</v>
+        <v>7046392</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5382,23 +5374,39 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5416,10 +5424,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067031</v>
+        <v>131067790</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5427,26 +5435,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5454,10 +5467,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466288</v>
+        <v>466313</v>
       </c>
       <c r="R39" t="n">
-        <v>7046458</v>
+        <v>7046432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5494,7 +5507,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På flera gamla granar i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5503,13 +5516,12 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5522,14 +5534,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5547,10 +5554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067032</v>
+        <v>131067789</v>
       </c>
       <c r="B40" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5558,26 +5565,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5585,10 +5597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466239</v>
+        <v>466317</v>
       </c>
       <c r="R40" t="n">
-        <v>7046392</v>
+        <v>7046435</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5623,19 +5635,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5648,14 +5664,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5673,32 +5684,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067789</v>
+        <v>131067006</v>
       </c>
       <c r="B41" t="n">
-        <v>57886</v>
+        <v>57076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5706,20 +5717,24 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466317</v>
+        <v>466180</v>
       </c>
       <c r="R41" t="n">
-        <v>7046435</v>
+        <v>7046368</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5756,7 +5771,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5771,21 +5786,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067787</v>
+        <v>131067035</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,31 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466335</v>
+        <v>466172</v>
       </c>
       <c r="R3" t="n">
-        <v>7046445</v>
+        <v>7046340</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,9 +912,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,7 +937,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067798</v>
+        <v>131067787</v>
       </c>
       <c r="B4" t="n">
         <v>57887</v>
@@ -979,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466279</v>
+        <v>466335</v>
       </c>
       <c r="R4" t="n">
-        <v>7046403</v>
+        <v>7046445</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1196,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067035</v>
+        <v>131067798</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,26 +1208,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1234,10 +1240,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466172</v>
+        <v>466279</v>
       </c>
       <c r="R6" t="n">
-        <v>7046340</v>
+        <v>7046403</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1280,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,13 +1289,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1302,14 +1307,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067786</v>
+        <v>131067030</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,31 +1726,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466366</v>
+        <v>466302</v>
       </c>
       <c r="R10" t="n">
-        <v>7046466</v>
+        <v>7046517</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1796,17 +1791,13 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1825,9 +1816,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1845,7 +1841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067792</v>
+        <v>131067786</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1878,7 +1874,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1888,10 +1884,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466356</v>
+        <v>466366</v>
       </c>
       <c r="R11" t="n">
-        <v>7046460</v>
+        <v>7046466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1928,7 +1924,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,14 +1951,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1980,7 +1971,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067781</v>
+        <v>131067792</v>
       </c>
       <c r="B12" t="n">
         <v>57887</v>
@@ -2013,7 +2004,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2023,10 +2014,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466204</v>
+        <v>466356</v>
       </c>
       <c r="R12" t="n">
-        <v>7046448</v>
+        <v>7046460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2063,7 +2054,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2077,7 +2068,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2090,9 +2081,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2110,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131067030</v>
+        <v>131067781</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,26 +2117,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2148,10 +2149,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466302</v>
+        <v>466204</v>
       </c>
       <c r="R13" t="n">
-        <v>7046517</v>
+        <v>7046448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2186,19 +2187,23 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2211,14 +2216,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067804</v>
+        <v>131067784</v>
       </c>
       <c r="B32" t="n">
         <v>57887</v>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466158</v>
+        <v>466379</v>
       </c>
       <c r="R32" t="n">
-        <v>7046307</v>
+        <v>7046479</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4659,14 +4659,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4684,7 +4679,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067784</v>
+        <v>131067804</v>
       </c>
       <c r="B33" t="n">
         <v>57887</v>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466379</v>
+        <v>466158</v>
       </c>
       <c r="R33" t="n">
-        <v>7046479</v>
+        <v>7046307</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4781,7 +4776,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4794,9 +4789,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5424,32 +5424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067790</v>
+        <v>131067006</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>57076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5457,20 +5457,24 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466313</v>
+        <v>466180</v>
       </c>
       <c r="R39" t="n">
-        <v>7046432</v>
+        <v>7046368</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5507,7 +5511,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5522,21 +5526,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5684,32 +5673,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067006</v>
+        <v>131067790</v>
       </c>
       <c r="B41" t="n">
-        <v>57076</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5717,24 +5706,20 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466180</v>
+        <v>466313</v>
       </c>
       <c r="R41" t="n">
-        <v>7046368</v>
+        <v>7046432</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5771,7 +5756,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5786,6 +5771,21 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067787</v>
+        <v>131067810</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,42 +948,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466335</v>
+        <v>466532</v>
       </c>
       <c r="R4" t="n">
-        <v>7046445</v>
+        <v>7046605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,21 +1043,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,7 +1060,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067788</v>
+        <v>131067787</v>
       </c>
       <c r="B5" t="n">
         <v>57887</v>
@@ -1110,10 +1103,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466325</v>
+        <v>466335</v>
       </c>
       <c r="R5" t="n">
-        <v>7046442</v>
+        <v>7046445</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1327,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067810</v>
+        <v>131067788</v>
       </c>
       <c r="B7" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,50 +1331,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466532</v>
+        <v>466325</v>
       </c>
       <c r="R7" t="n">
-        <v>7046605</v>
+        <v>7046442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,7 +1403,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,6 +1418,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -4549,7 +4549,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067784</v>
+        <v>131067804</v>
       </c>
       <c r="B32" t="n">
         <v>57887</v>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466379</v>
+        <v>466158</v>
       </c>
       <c r="R32" t="n">
-        <v>7046479</v>
+        <v>7046307</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4659,9 +4659,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4679,7 +4684,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067804</v>
+        <v>131067784</v>
       </c>
       <c r="B33" t="n">
         <v>57887</v>
@@ -4722,10 +4727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466158</v>
+        <v>466379</v>
       </c>
       <c r="R33" t="n">
-        <v>7046307</v>
+        <v>7046479</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4776,7 +4781,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4789,14 +4794,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5424,32 +5424,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067006</v>
+        <v>131067790</v>
       </c>
       <c r="B39" t="n">
-        <v>57076</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5457,24 +5457,20 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466180</v>
+        <v>466313</v>
       </c>
       <c r="R39" t="n">
-        <v>7046368</v>
+        <v>7046432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5511,7 +5507,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5526,6 +5522,21 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5673,32 +5684,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067790</v>
+        <v>131067006</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>57076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5706,20 +5717,24 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466313</v>
+        <v>466180</v>
       </c>
       <c r="R41" t="n">
-        <v>7046432</v>
+        <v>7046368</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5756,7 +5771,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5771,21 +5786,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131067036</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131067035</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067810</v>
+        <v>131067787</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,50 +948,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466532</v>
+        <v>466335</v>
       </c>
       <c r="R4" t="n">
-        <v>7046605</v>
+        <v>7046445</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1020,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,6 +1035,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067787</v>
+        <v>131067798</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1110,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466335</v>
+        <v>466279</v>
       </c>
       <c r="R5" t="n">
-        <v>7046445</v>
+        <v>7046403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,7 +1164,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1190,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067798</v>
+        <v>131067788</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,10 +1240,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466279</v>
+        <v>466325</v>
       </c>
       <c r="R6" t="n">
-        <v>7046403</v>
+        <v>7046442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1294,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1320,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067788</v>
+        <v>131067810</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>58047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,42 +1338,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466325</v>
+        <v>466532</v>
       </c>
       <c r="R7" t="n">
-        <v>7046442</v>
+        <v>7046605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,7 +1418,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,21 +1433,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
         <v>131067801</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>131067000</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131067030</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>131067786</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>131067792</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>131067781</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>131067800</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>131067795</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131067799</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>131067783</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>131067805</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>131067802</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>131067791</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>131067794</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>131067782</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>131067803</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>131067796</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>131067453</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067038</v>
+        <v>131067797</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3937,26 +3937,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3964,10 +3969,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466024</v>
+        <v>466283</v>
       </c>
       <c r="R27" t="n">
-        <v>7046276</v>
+        <v>7046407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4004,7 +4009,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4013,7 +4018,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4032,14 +4036,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4057,10 +4056,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067797</v>
+        <v>131067806</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4090,7 +4089,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4100,10 +4099,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466283</v>
+        <v>466140</v>
       </c>
       <c r="R28" t="n">
-        <v>7046407</v>
+        <v>7046291</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4140,7 +4139,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4167,9 +4166,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4187,10 +4191,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067806</v>
+        <v>131067038</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4198,31 +4202,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4230,10 +4229,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466140</v>
+        <v>466024</v>
       </c>
       <c r="R29" t="n">
-        <v>7046291</v>
+        <v>7046276</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4270,7 +4269,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4279,6 +4278,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4299,12 +4299,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4325,7 +4325,7 @@
         <v>131067452</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067033</v>
+        <v>131067784</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4449,26 +4449,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4476,10 +4481,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466193</v>
+        <v>466379</v>
       </c>
       <c r="R31" t="n">
-        <v>7046386</v>
+        <v>7046479</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4516,7 +4521,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4525,13 +4530,27 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4549,10 +4568,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067804</v>
+        <v>131067793</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4592,10 +4611,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466158</v>
+        <v>466303</v>
       </c>
       <c r="R32" t="n">
-        <v>7046307</v>
+        <v>7046416</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4659,14 +4678,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4684,10 +4698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067784</v>
+        <v>131067033</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4695,31 +4709,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4727,10 +4736,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466379</v>
+        <v>466193</v>
       </c>
       <c r="R33" t="n">
-        <v>7046479</v>
+        <v>7046386</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4767,7 +4776,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4776,27 +4785,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4814,10 +4809,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067793</v>
+        <v>131067804</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4857,10 +4852,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466303</v>
+        <v>466158</v>
       </c>
       <c r="R34" t="n">
-        <v>7046416</v>
+        <v>7046307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4924,9 +4919,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4947,7 +4947,7 @@
         <v>131067037</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>131067451</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>131067031</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>131067032</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>131067790</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>131067789</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067035</v>
+        <v>131067787</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +817,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466172</v>
+        <v>466335</v>
       </c>
       <c r="R3" t="n">
-        <v>7046340</v>
+        <v>7046445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +898,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,14 +916,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,7 +936,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067787</v>
+        <v>131067798</v>
       </c>
       <c r="B4" t="n">
         <v>57888</v>
@@ -980,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466335</v>
+        <v>466279</v>
       </c>
       <c r="R4" t="n">
-        <v>7046445</v>
+        <v>7046403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,7 +1033,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1067,7 +1066,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067798</v>
+        <v>131067788</v>
       </c>
       <c r="B5" t="n">
         <v>57888</v>
@@ -1110,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466279</v>
+        <v>466325</v>
       </c>
       <c r="R5" t="n">
-        <v>7046403</v>
+        <v>7046442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1164,7 +1163,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1197,10 +1196,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067788</v>
+        <v>131067810</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>58047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,42 +1207,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466325</v>
+        <v>466532</v>
       </c>
       <c r="R6" t="n">
-        <v>7046442</v>
+        <v>7046605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1287,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,21 +1302,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1327,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067810</v>
+        <v>131067035</v>
       </c>
       <c r="B7" t="n">
-        <v>58047</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,50 +1330,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466532</v>
+        <v>466172</v>
       </c>
       <c r="R7" t="n">
-        <v>7046605</v>
+        <v>7046340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,7 +1397,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,12 +1406,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067797</v>
+        <v>131067806</v>
       </c>
       <c r="B27" t="n">
         <v>57888</v>
@@ -3959,7 +3959,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466283</v>
+        <v>466140</v>
       </c>
       <c r="R27" t="n">
-        <v>7046407</v>
+        <v>7046291</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4036,9 +4036,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4056,10 +4061,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067806</v>
+        <v>131067038</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4067,31 +4072,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466140</v>
+        <v>466024</v>
       </c>
       <c r="R28" t="n">
-        <v>7046291</v>
+        <v>7046276</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4148,6 +4148,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4168,12 +4169,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4191,10 +4192,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067038</v>
+        <v>131067797</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4202,26 +4203,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4229,10 +4235,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466024</v>
+        <v>466283</v>
       </c>
       <c r="R29" t="n">
-        <v>7046276</v>
+        <v>7046407</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4269,7 +4275,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4278,7 +4284,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4297,14 +4302,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067784</v>
+        <v>131067804</v>
       </c>
       <c r="B31" t="n">
         <v>57888</v>
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466379</v>
+        <v>466158</v>
       </c>
       <c r="R31" t="n">
-        <v>7046479</v>
+        <v>7046307</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4548,9 +4548,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4568,7 +4573,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067793</v>
+        <v>131067784</v>
       </c>
       <c r="B32" t="n">
         <v>57888</v>
@@ -4611,10 +4616,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466303</v>
+        <v>466379</v>
       </c>
       <c r="R32" t="n">
-        <v>7046416</v>
+        <v>7046479</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4665,7 +4670,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4698,10 +4703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067033</v>
+        <v>131067793</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4709,26 +4714,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4736,10 +4746,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466193</v>
+        <v>466303</v>
       </c>
       <c r="R33" t="n">
-        <v>7046386</v>
+        <v>7046416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4776,7 +4786,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4785,13 +4795,27 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4809,10 +4833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067804</v>
+        <v>131067033</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4820,31 +4844,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4852,10 +4871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466158</v>
+        <v>466193</v>
       </c>
       <c r="R34" t="n">
-        <v>7046307</v>
+        <v>7046386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4892,7 +4911,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4901,32 +4920,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131067036</v>
+        <v>131067031</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466113</v>
+        <v>466288</v>
       </c>
       <c r="R2" t="n">
-        <v>7046326</v>
+        <v>7046458</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>På flera gamla granar i granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,42 +806,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131067787</v>
+        <v>131067032</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466335</v>
+        <v>466239</v>
       </c>
       <c r="R3" t="n">
-        <v>7046445</v>
+        <v>7046392</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,23 +882,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -916,9 +907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,42 +932,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131067798</v>
+        <v>131067033</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466279</v>
+        <v>466193</v>
       </c>
       <c r="R4" t="n">
-        <v>7046403</v>
+        <v>7046386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1010,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,27 +1019,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,42 +1043,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131067788</v>
+        <v>131067035</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466325</v>
+        <v>466172</v>
       </c>
       <c r="R5" t="n">
-        <v>7046442</v>
+        <v>7046340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,6 +1130,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1176,9 +1149,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1196,61 +1174,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131067810</v>
+        <v>131067036</v>
       </c>
       <c r="B6" t="n">
-        <v>58047</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466532</v>
+        <v>466113</v>
       </c>
       <c r="R6" t="n">
-        <v>7046605</v>
+        <v>7046326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1252,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,12 +1261,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,14 +1305,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131067035</v>
+        <v>131067037</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1357,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466172</v>
+        <v>466097</v>
       </c>
       <c r="R7" t="n">
-        <v>7046340</v>
+        <v>7046282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,7 +1383,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,27 +1398,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1450,42 +1416,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131067801</v>
+        <v>131067038</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1493,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466250</v>
+        <v>466024</v>
       </c>
       <c r="R8" t="n">
-        <v>7046376</v>
+        <v>7046276</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1533,7 +1494,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,6 +1503,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1560,9 +1522,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1580,53 +1547,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131067000</v>
+        <v>131067451</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466110</v>
+        <v>466178</v>
       </c>
       <c r="R9" t="n">
-        <v>7046316</v>
+        <v>7046388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1656,14 +1615,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran med full längd.</t>
+          <t>Gran, någon bål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,55 +1643,30 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131067030</v>
+        <v>131067452</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1749,14 +1693,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466302</v>
+        <v>466252</v>
       </c>
       <c r="R10" t="n">
-        <v>7046517</v>
+        <v>7046439</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1786,9 +1730,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1801,93 +1760,63 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131067786</v>
+        <v>131067453</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långan Öst, Jmt</t>
+          <t>Åbogen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466366</v>
+        <v>466258</v>
       </c>
       <c r="R11" t="n">
-        <v>7046466</v>
+        <v>7046494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1917,14 +1846,24 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,48 +1872,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131067792</v>
+        <v>131067000</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2004,7 +1924,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2014,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>466356</v>
+        <v>466110</v>
       </c>
       <c r="R12" t="n">
-        <v>7046460</v>
+        <v>7046316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,7 +1974,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,7 +1988,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2083,12 +2003,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2109,7 +2029,7 @@
         <v>131067781</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2236,10 +2156,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131067800</v>
+        <v>131067795</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2279,10 +2199,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466272</v>
+        <v>466291</v>
       </c>
       <c r="R14" t="n">
-        <v>7046391</v>
+        <v>7046411</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2346,14 +2266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2371,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131067795</v>
+        <v>131067796</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2414,10 +2329,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466291</v>
+        <v>466290</v>
       </c>
       <c r="R15" t="n">
-        <v>7046411</v>
+        <v>7046409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2481,9 +2396,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2501,10 +2421,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131067799</v>
+        <v>131067797</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,10 +2464,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466278</v>
+        <v>466283</v>
       </c>
       <c r="R16" t="n">
-        <v>7046398</v>
+        <v>7046407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2631,32 +2551,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131067005</v>
+        <v>131067798</v>
       </c>
       <c r="B17" t="n">
-        <v>57076</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2664,24 +2584,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466351</v>
+        <v>466279</v>
       </c>
       <c r="R17" t="n">
-        <v>7046569</v>
+        <v>7046403</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2718,7 +2634,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2732,7 +2648,22 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2750,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131067783</v>
+        <v>131067799</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,10 +2724,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466431</v>
+        <v>466278</v>
       </c>
       <c r="R18" t="n">
-        <v>7046517</v>
+        <v>7046398</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2847,7 +2778,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2880,10 +2811,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131067805</v>
+        <v>131067800</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2923,10 +2854,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466148</v>
+        <v>466272</v>
       </c>
       <c r="R19" t="n">
-        <v>7046298</v>
+        <v>7046391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3015,10 +2946,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131067802</v>
+        <v>131067801</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,10 +2989,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466202</v>
+        <v>466250</v>
       </c>
       <c r="R20" t="n">
-        <v>7046342</v>
+        <v>7046376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3125,14 +3056,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3150,10 +3076,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131067791</v>
+        <v>131067802</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3193,10 +3119,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466309</v>
+        <v>466202</v>
       </c>
       <c r="R21" t="n">
-        <v>7046427</v>
+        <v>7046342</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3247,7 +3173,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3260,9 +3186,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3280,10 +3211,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131067794</v>
+        <v>131067803</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3323,10 +3254,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466295</v>
+        <v>466227</v>
       </c>
       <c r="R22" t="n">
-        <v>7046414</v>
+        <v>7046368</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3390,9 +3321,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3346,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131067782</v>
+        <v>131067804</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3453,10 +3389,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466553</v>
+        <v>466158</v>
       </c>
       <c r="R23" t="n">
-        <v>7046611</v>
+        <v>7046307</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3507,7 +3443,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3520,9 +3456,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3540,10 +3481,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131067803</v>
+        <v>131067805</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3583,10 +3524,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466227</v>
+        <v>466148</v>
       </c>
       <c r="R24" t="n">
-        <v>7046368</v>
+        <v>7046298</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3675,10 +3616,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131067796</v>
+        <v>131067806</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3708,7 +3649,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3718,10 +3659,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466290</v>
+        <v>466140</v>
       </c>
       <c r="R25" t="n">
-        <v>7046409</v>
+        <v>7046291</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3758,7 +3699,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3810,48 +3751,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131067453</v>
+        <v>131067006</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466258</v>
+        <v>466180</v>
       </c>
       <c r="R26" t="n">
-        <v>7046494</v>
+        <v>7046368</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3881,24 +3831,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:39</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3907,61 +3847,60 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131067806</v>
+        <v>131067030</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3969,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466140</v>
+        <v>466302</v>
       </c>
       <c r="R27" t="n">
-        <v>7046291</v>
+        <v>7046517</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4007,23 +3946,19 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4038,12 +3973,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4061,10 +3996,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131067038</v>
+        <v>131067782</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4072,26 +4007,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4099,10 +4039,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466024</v>
+        <v>466553</v>
       </c>
       <c r="R28" t="n">
-        <v>7046276</v>
+        <v>7046611</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4139,7 +4079,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4148,13 +4088,12 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4167,14 +4106,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4192,10 +4126,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131067797</v>
+        <v>131067783</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4235,10 +4169,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466283</v>
+        <v>466431</v>
       </c>
       <c r="R29" t="n">
-        <v>7046407</v>
+        <v>7046517</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4289,7 +4223,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4322,10 +4256,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131067452</v>
+        <v>131067784</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4333,37 +4267,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466252</v>
+        <v>466379</v>
       </c>
       <c r="R30" t="n">
-        <v>7046439</v>
+        <v>7046479</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4393,24 +4332,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4419,29 +4348,48 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131067804</v>
+        <v>131067786</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4481,10 +4429,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466158</v>
+        <v>466366</v>
       </c>
       <c r="R31" t="n">
-        <v>7046307</v>
+        <v>7046466</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4535,7 +4483,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4548,14 +4496,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4573,10 +4516,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131067784</v>
+        <v>131067787</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4616,10 +4559,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466379</v>
+        <v>466335</v>
       </c>
       <c r="R32" t="n">
-        <v>7046479</v>
+        <v>7046445</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4703,10 +4646,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131067793</v>
+        <v>131067788</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4746,10 +4689,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466303</v>
+        <v>466325</v>
       </c>
       <c r="R33" t="n">
-        <v>7046416</v>
+        <v>7046442</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4800,7 +4743,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4833,10 +4776,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131067033</v>
+        <v>131067789</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4844,26 +4787,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4871,10 +4819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466193</v>
+        <v>466317</v>
       </c>
       <c r="R34" t="n">
-        <v>7046386</v>
+        <v>7046435</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4911,7 +4859,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4920,13 +4868,27 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4944,10 +4906,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131067037</v>
+        <v>131067790</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4955,26 +4917,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4982,10 +4949,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466097</v>
+        <v>466313</v>
       </c>
       <c r="R35" t="n">
-        <v>7046282</v>
+        <v>7046432</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5022,7 +4989,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5031,13 +4998,27 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5055,10 +5036,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131067451</v>
+        <v>131067791</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5066,34 +5047,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åbogen, Jmt</t>
+          <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466178</v>
+        <v>466309</v>
       </c>
       <c r="R36" t="n">
-        <v>7046388</v>
+        <v>7046427</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5123,24 +5112,14 @@
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gran, någon bål</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5151,26 +5130,46 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131067031</v>
+        <v>131067792</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5178,26 +5177,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5205,10 +5209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466288</v>
+        <v>466356</v>
       </c>
       <c r="R37" t="n">
-        <v>7046458</v>
+        <v>7046460</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5245,7 +5249,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera gamla granar i granskog.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5254,13 +5258,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5275,12 +5278,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5298,10 +5301,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131067032</v>
+        <v>131067793</v>
       </c>
       <c r="B38" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5309,26 +5312,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5336,10 +5344,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466239</v>
+        <v>466303</v>
       </c>
       <c r="R38" t="n">
-        <v>7046392</v>
+        <v>7046416</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5374,13 +5382,17 @@
           <t>2026-02-07</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5399,14 +5411,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5424,10 +5431,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131067790</v>
+        <v>131067794</v>
       </c>
       <c r="B39" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5467,10 +5474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466313</v>
+        <v>466295</v>
       </c>
       <c r="R39" t="n">
-        <v>7046432</v>
+        <v>7046414</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5521,7 +5528,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5554,32 +5561,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131067789</v>
+        <v>131067005</v>
       </c>
       <c r="B40" t="n">
-        <v>57888</v>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5587,20 +5594,24 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långan Öst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466317</v>
+        <v>466351</v>
       </c>
       <c r="R40" t="n">
-        <v>7046435</v>
+        <v>7046569</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5637,7 +5648,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Färsk spillning ovanpå snötäcket under en tall.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5652,21 +5663,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5684,40 +5680,44 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131067006</v>
+        <v>131067810</v>
       </c>
       <c r="B41" t="n">
-        <v>57076</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466180</v>
+        <v>466532</v>
       </c>
       <c r="R41" t="n">
-        <v>7046368</v>
+        <v>7046605</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket under en tall i barrblandskog.</t>
+          <t>Två födosökande talltitor i äldre barrskog med flerskiktning och murknande björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 773-2024 artfynd.xlsx
+++ b/artfynd/A 773-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -929,6 +939,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1055,6 +1070,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067032</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067033</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067035</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067036</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1539,6 +1574,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067037</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1670,6 +1710,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067038</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1782,6 +1827,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067451</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1898,6 +1948,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067452</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2014,6 +2069,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067453</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2149,6 +2209,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067000</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2279,6 +2344,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067781</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2409,6 +2479,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067782</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2539,6 +2614,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2669,6 +2749,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067784</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2799,6 +2884,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067786</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2929,6 +3019,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067787</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3059,6 +3154,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067788</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3189,6 +3289,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067789</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3319,6 +3424,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067790</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3449,6 +3559,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067791</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3584,6 +3699,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067792</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3714,6 +3834,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067793</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3844,6 +3969,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067794</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3974,6 +4104,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067795</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4109,6 +4244,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067796</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4239,6 +4379,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067797</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4369,6 +4514,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067798</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4499,6 +4649,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067799</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4634,6 +4789,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067800</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4764,6 +4924,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067801</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4899,6 +5064,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067802</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5034,6 +5204,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067803</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5169,6 +5344,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067804</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5304,6 +5484,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067805</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5439,6 +5624,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067806</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5558,6 +5748,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067005</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5677,6 +5872,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067006</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5800,8 +6000,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131067810</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>